--- a/base_datas/mediana_uf_detalhamento.xlsx
+++ b/base_datas/mediana_uf_detalhamento.xlsx
@@ -612,7 +612,7 @@
         <v>4369.811811135316</v>
       </c>
       <c r="E2">
-        <v>95.98708203625677</v>
+        <v>95.98708203625709</v>
       </c>
       <c r="F2">
         <v>252.0553078843906</v>
@@ -733,7 +733,7 @@
         <v>7156.514930238858</v>
       </c>
       <c r="E3">
-        <v>214.0420135933441</v>
+        <v>214.0420135933431</v>
       </c>
       <c r="F3">
         <v>274.5102338704621</v>
@@ -851,28 +851,28 @@
         </is>
       </c>
       <c r="B4">
-        <v>169.8064010692379</v>
+        <v>171.4495354415199</v>
       </c>
       <c r="C4">
-        <v>43.65199646531591</v>
+        <v>43.67014018281431</v>
       </c>
       <c r="D4">
-        <v>5725.178745227417</v>
+        <v>5726.688700334822</v>
       </c>
       <c r="E4">
-        <v>71.25180257192504</v>
+        <v>74.19200403963896</v>
       </c>
       <c r="F4">
-        <v>157.4726792852417</v>
+        <v>158.9068442782159</v>
       </c>
       <c r="G4">
-        <v>3.165660261448537</v>
+        <v>3.183608649052902</v>
       </c>
       <c r="H4">
         <v>26.06852641528153</v>
       </c>
       <c r="I4">
-        <v>84.77904721401977</v>
+        <v>85.01069899615625</v>
       </c>
       <c r="J4">
         <v>12.3110447320021</v>
@@ -881,16 +881,16 @@
         <v>3.592267206884112E-15</v>
       </c>
       <c r="L4">
-        <v>3782.277518488781</v>
+        <v>3790.868806863133</v>
       </c>
       <c r="M4">
-        <v>898.6154481739363</v>
+        <v>910.0679691326828</v>
       </c>
       <c r="N4">
-        <v>965.3614312497921</v>
+        <v>971.8157797316064</v>
       </c>
       <c r="O4">
-        <v>61.95763093029097</v>
+        <v>62.95594416335381</v>
       </c>
       <c r="P4">
         <v>9.68390660008944</v>
@@ -899,31 +899,31 @@
         <v>0.001101146161570692</v>
       </c>
       <c r="S4">
-        <v>0.3587623593598979</v>
+        <v>0.3591155395638378</v>
       </c>
       <c r="T4">
-        <v>1.220564166059237</v>
+        <v>1.397097140806316</v>
       </c>
       <c r="U4">
         <v>0.8978670076726343</v>
       </c>
       <c r="V4">
-        <v>63.03933504483657</v>
+        <v>63.4056931802269</v>
       </c>
       <c r="W4">
-        <v>86.19288638423185</v>
+        <v>86.21377448775101</v>
       </c>
       <c r="Z4">
         <v>1.175378078923063E-14</v>
       </c>
       <c r="AA4">
-        <v>1.964530800357446</v>
+        <v>2.016453615085757</v>
       </c>
       <c r="AB4">
-        <v>1.315701619778346</v>
+        <v>1.343842721424028</v>
       </c>
       <c r="AC4">
-        <v>8.872686227724777E-17</v>
+        <v>1.388432990467504E-16</v>
       </c>
       <c r="AE4">
         <v>0.1920357684463735</v>
@@ -935,31 +935,31 @@
         <v>46.61364158392152</v>
       </c>
       <c r="AH4">
-        <v>1397.370823905824</v>
+        <v>1410.287652265358</v>
       </c>
       <c r="AJ4">
-        <v>33.18155770333667</v>
+        <v>33.07058824343207</v>
       </c>
       <c r="AK4">
-        <v>960.2376345944492</v>
+        <v>963.1955948395524</v>
       </c>
       <c r="AL4">
-        <v>157.4943072988632</v>
+        <v>158.8983870967742</v>
       </c>
       <c r="AM4">
-        <v>759.1673482805024</v>
+        <v>770.5769718752455</v>
       </c>
       <c r="AN4">
-        <v>29.44907168162823</v>
+        <v>29.69305645474557</v>
       </c>
       <c r="AO4">
-        <v>53.76942589788913</v>
+        <v>53.80591680414802</v>
       </c>
       <c r="AP4">
-        <v>754.9617747688144</v>
+        <v>758.7336029077692</v>
       </c>
       <c r="AQ4">
-        <v>6.751457685831065</v>
+        <v>6.823548245087445</v>
       </c>
       <c r="AR4">
         <v>61.93428067751761</v>
@@ -968,10 +968,10 @@
         <v>39.08398145965904</v>
       </c>
       <c r="AT4">
-        <v>6.886431356723794</v>
+        <v>6.92083648846484</v>
       </c>
       <c r="AU4">
-        <v>22.36866533173394</v>
+        <v>21.64721909016769</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -993,7 +993,7 @@
         <v>5609.384104910445</v>
       </c>
       <c r="E5">
-        <v>172.4607249238737</v>
+        <v>172.4607249238739</v>
       </c>
       <c r="F5">
         <v>405.2196854783878</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>320.2118049689144</v>
+        <v>320.2355646609213</v>
       </c>
       <c r="C6">
-        <v>34.33856224325772</v>
+        <v>34.7884331558901</v>
       </c>
       <c r="D6">
-        <v>5365.508380461019</v>
+        <v>5367.861516606124</v>
       </c>
       <c r="E6">
-        <v>83.33969335807183</v>
+        <v>83.79119931792346</v>
       </c>
       <c r="F6">
-        <v>294.998714320504</v>
+        <v>295.0768123741239</v>
       </c>
       <c r="G6">
-        <v>15.70256886760692</v>
+        <v>15.7278222844149</v>
       </c>
       <c r="H6">
         <v>9.845618549563504</v>
@@ -1135,22 +1135,22 @@
         <v>187.5633839444355</v>
       </c>
       <c r="J6">
-        <v>29.91768848859997</v>
+        <v>29.93780144700761</v>
       </c>
       <c r="K6">
         <v>3.311015979150592E-15</v>
       </c>
       <c r="L6">
-        <v>3750.143036022394</v>
+        <v>3750.485259072385</v>
       </c>
       <c r="M6">
-        <v>577.3547533346373</v>
+        <v>577.5237782793272</v>
       </c>
       <c r="N6">
-        <v>971.048395873335</v>
+        <v>971.4157599376458</v>
       </c>
       <c r="O6">
-        <v>46.02889006016961</v>
+        <v>46.03345351169262</v>
       </c>
       <c r="P6">
         <v>13.95828267013427</v>
@@ -1162,31 +1162,31 @@
         <v>0.2392146017699115</v>
       </c>
       <c r="S6">
-        <v>8.601605241006173</v>
+        <v>8.636247777118264</v>
       </c>
       <c r="T6">
-        <v>9.945061131264275</v>
+        <v>9.965139822898013</v>
       </c>
       <c r="U6">
-        <v>6.360471944077084</v>
+        <v>6.384898569019356</v>
       </c>
       <c r="V6">
-        <v>109.4936022677715</v>
+        <v>109.5169194291377</v>
       </c>
       <c r="W6">
-        <v>140.7074450345173</v>
+        <v>140.9219181337077</v>
       </c>
       <c r="Z6">
-        <v>2.005890717487678E-14</v>
+        <v>2.013235137517247E-14</v>
       </c>
       <c r="AA6">
-        <v>12.91350257281633</v>
+        <v>12.93256388195819</v>
       </c>
       <c r="AB6">
-        <v>1.808872991421456</v>
+        <v>1.841709009009009</v>
       </c>
       <c r="AC6">
-        <v>2.136970633864963E-16</v>
+        <v>2.314539162353673E-16</v>
       </c>
       <c r="AD6">
         <v>0.3205167475609768</v>
@@ -1201,43 +1201,43 @@
         <v>0.05929532381892133</v>
       </c>
       <c r="AH6">
-        <v>2038.514846017395</v>
+        <v>2039.403941236069</v>
       </c>
       <c r="AJ6">
-        <v>42.32926842335591</v>
+        <v>42.36238551005573</v>
       </c>
       <c r="AK6">
-        <v>612.8537552742615</v>
+        <v>613.2409758444574</v>
       </c>
       <c r="AL6">
-        <v>145.9426845585965</v>
+        <v>145.9845109764977</v>
       </c>
       <c r="AM6">
-        <v>612.3468730539105</v>
+        <v>612.8119484978541</v>
       </c>
       <c r="AN6">
-        <v>30.40439614783967</v>
+        <v>30.40461551267389</v>
       </c>
       <c r="AO6">
-        <v>37.93062807982367</v>
+        <v>38.00225514505285</v>
       </c>
       <c r="AP6">
-        <v>447.8478569364271</v>
+        <v>448.5965185935465</v>
       </c>
       <c r="AQ6">
-        <v>35.83924752627318</v>
+        <v>35.86217789804469</v>
       </c>
       <c r="AR6">
-        <v>12.59225242294288</v>
+        <v>12.59989763867856</v>
       </c>
       <c r="AS6">
-        <v>9.103132743219202</v>
+        <v>9.111792478726324</v>
       </c>
       <c r="AT6">
         <v>0.9002602233814221</v>
       </c>
       <c r="AU6">
-        <v>30.42467224475259</v>
+        <v>30.48694686411146</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1259,7 +1259,7 @@
         <v>5305.907318049677</v>
       </c>
       <c r="E7">
-        <v>130.9452868118297</v>
+        <v>130.9452868118303</v>
       </c>
       <c r="F7">
         <v>236.4749385590393</v>
@@ -1389,7 +1389,7 @@
         <v>2372.308437906705</v>
       </c>
       <c r="E8">
-        <v>1442.628285151825</v>
+        <v>1442.628285151826</v>
       </c>
       <c r="F8">
         <v>8141.057707744824</v>
@@ -1504,7 +1504,7 @@
         <v>5736.585227237649</v>
       </c>
       <c r="E9">
-        <v>310.4166384766984</v>
+        <v>310.4166384766983</v>
       </c>
       <c r="F9">
         <v>471.7497120885447</v>
@@ -1643,7 +1643,7 @@
         <v>6482.011595172992</v>
       </c>
       <c r="E10">
-        <v>252.6878592869401</v>
+        <v>252.6878592869402</v>
       </c>
       <c r="F10">
         <v>626.5241840068309</v>
@@ -1782,7 +1782,7 @@
         <v>5735.313998647029</v>
       </c>
       <c r="E11">
-        <v>59.25458393113386</v>
+        <v>59.25458393113343</v>
       </c>
       <c r="F11">
         <v>224.7458281563605</v>
@@ -1906,19 +1906,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>401.3003411458333</v>
+        <v>402.7304086538462</v>
       </c>
       <c r="C12">
         <v>84.73742657996118</v>
       </c>
       <c r="D12">
-        <v>5649.094768583954</v>
+        <v>5649.930893059436</v>
       </c>
       <c r="E12">
-        <v>216.7255998713403</v>
+        <v>216.7255998713413</v>
       </c>
       <c r="F12">
-        <v>365.4418425197322</v>
+        <v>365.7233051090701</v>
       </c>
       <c r="G12">
         <v>28.309695604436</v>
@@ -1936,16 +1936,16 @@
         <v>6.995114383095253E-15</v>
       </c>
       <c r="L12">
-        <v>3331.5168645539</v>
+        <v>3331.579066723574</v>
       </c>
       <c r="M12">
-        <v>1404.506385473263</v>
+        <v>1405.856329956681</v>
       </c>
       <c r="N12">
-        <v>720.4192795717797</v>
+        <v>720.4474850102858</v>
       </c>
       <c r="O12">
-        <v>145.9890438018895</v>
+        <v>146.0059116110176</v>
       </c>
       <c r="P12">
         <v>8.422994657163855</v>
@@ -1957,22 +1957,22 @@
         <v>6.204903737259343</v>
       </c>
       <c r="S12">
-        <v>20.60194078128936</v>
+        <v>20.95589621518707</v>
       </c>
       <c r="T12">
-        <v>36.40612586545417</v>
+        <v>36.43270115165102</v>
       </c>
       <c r="U12">
-        <v>38.20083844317679</v>
+        <v>38.22881944444444</v>
       </c>
       <c r="V12">
-        <v>135.1238270418668</v>
+        <v>135.3074793697066</v>
       </c>
       <c r="W12">
-        <v>123.2157023495776</v>
+        <v>123.2790281226928</v>
       </c>
       <c r="Z12">
-        <v>9.504843388874495E-15</v>
+        <v>9.627435171277063E-15</v>
       </c>
       <c r="AA12">
         <v>10.26497872932795</v>
@@ -1996,43 +1996,43 @@
         <v>0.1726096232665207</v>
       </c>
       <c r="AH12">
-        <v>2374.824221519485</v>
+        <v>2378.944964111766</v>
       </c>
       <c r="AJ12">
-        <v>65.27318021260946</v>
+        <v>65.30754430878299</v>
       </c>
       <c r="AK12">
-        <v>529.8168154761905</v>
+        <v>530.6119159678335</v>
       </c>
       <c r="AL12">
-        <v>74.6037973273942</v>
+        <v>74.60757269065817</v>
       </c>
       <c r="AM12">
         <v>16.47411006930427</v>
       </c>
       <c r="AN12">
-        <v>28.40502212347666</v>
+        <v>28.41652603231598</v>
       </c>
       <c r="AO12">
-        <v>32.46677179899119</v>
+        <v>32.55073184451818</v>
       </c>
       <c r="AP12">
-        <v>857.0910966497951</v>
+        <v>859.0280915090807</v>
       </c>
       <c r="AQ12">
-        <v>168.3869804547268</v>
+        <v>168.4825702562026</v>
       </c>
       <c r="AR12">
-        <v>192.6964808601134</v>
+        <v>192.8260907565258</v>
       </c>
       <c r="AS12">
-        <v>9.943244381211668</v>
+        <v>9.951911676467059</v>
       </c>
       <c r="AT12">
-        <v>1.27768298903341</v>
+        <v>1.252183200190869</v>
       </c>
       <c r="AU12">
-        <v>97.62967393561809</v>
+        <v>97.73072417646608</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>6927.244836198987</v>
       </c>
       <c r="E13">
-        <v>320.7798364008183</v>
+        <v>320.779836400818</v>
       </c>
       <c r="F13">
         <v>1024.156940294393</v>
@@ -2190,7 +2190,7 @@
         <v>7274.423909405655</v>
       </c>
       <c r="E14">
-        <v>416.8426244252089</v>
+        <v>416.8426244252096</v>
       </c>
       <c r="F14">
         <v>947.4007357723577</v>
@@ -2326,7 +2326,7 @@
         <v>4979.452091530481</v>
       </c>
       <c r="E15">
-        <v>53.33944761678157</v>
+        <v>53.33944761678166</v>
       </c>
       <c r="F15">
         <v>282.475778079864</v>
@@ -2459,7 +2459,7 @@
         <v>6246.753892109907</v>
       </c>
       <c r="E16">
-        <v>130.0366677033113</v>
+        <v>130.0366677033121</v>
       </c>
       <c r="F16">
         <v>234.3823215586307</v>
@@ -2586,7 +2586,7 @@
         <v>4748.423195951424</v>
       </c>
       <c r="E17">
-        <v>128.5714363266027</v>
+        <v>128.5714363266023</v>
       </c>
       <c r="F17">
         <v>214.5216456859791</v>
@@ -2716,7 +2716,7 @@
         <v>6543.778237644254</v>
       </c>
       <c r="E18">
-        <v>135.5227392872254</v>
+        <v>135.5227392872252</v>
       </c>
       <c r="F18">
         <v>286.7828499891139</v>
@@ -2843,7 +2843,7 @@
         <v>6141.010663941129</v>
       </c>
       <c r="E19">
-        <v>382.5710962508213</v>
+        <v>382.5710962508222</v>
       </c>
       <c r="F19">
         <v>643.9961210343909</v>
@@ -2852,22 +2852,22 @@
         <v>68.18604724456924</v>
       </c>
       <c r="H19">
-        <v>1.167434799309154</v>
+        <v>1.166587733333333</v>
       </c>
       <c r="I19">
         <v>264.2445316570177</v>
       </c>
       <c r="J19">
-        <v>89.41902221804276</v>
+        <v>89.72126816908921</v>
       </c>
       <c r="K19">
-        <v>1.030714691227961E-14</v>
+        <v>9.659619708916532E-15</v>
       </c>
       <c r="L19">
         <v>3222.969769654482</v>
       </c>
       <c r="M19">
-        <v>1883.39394278607</v>
+        <v>1897.418852068839</v>
       </c>
       <c r="N19">
         <v>846.0090025878803</v>
@@ -2891,7 +2891,7 @@
         <v>107.4086381268073</v>
       </c>
       <c r="U19">
-        <v>90.32612573218462</v>
+        <v>89.85737694103113</v>
       </c>
       <c r="V19">
         <v>174.1517608382437</v>
@@ -2918,22 +2918,22 @@
         <v>2.785638105818637</v>
       </c>
       <c r="AG19">
-        <v>1.097157080586214</v>
+        <v>1.028764598929768</v>
       </c>
       <c r="AH19">
-        <v>2375.357483631871</v>
+        <v>2379.198159325721</v>
       </c>
       <c r="AJ19">
-        <v>52.00706158441189</v>
+        <v>52.00429875838725</v>
       </c>
       <c r="AK19">
-        <v>370.5158020627606</v>
+        <v>370.711024930748</v>
       </c>
       <c r="AL19">
-        <v>87.88577772122909</v>
+        <v>88.11218003412969</v>
       </c>
       <c r="AM19">
-        <v>19.43765595463138</v>
+        <v>19.4499216137737</v>
       </c>
       <c r="AN19">
         <v>23.44991979355559</v>
@@ -2942,19 +2942,19 @@
         <v>140.8388710378667</v>
       </c>
       <c r="AP19">
-        <v>1498.307835328905</v>
+        <v>1498.63487384506</v>
       </c>
       <c r="AQ19">
-        <v>206.623787835111</v>
+        <v>206.8805238448421</v>
       </c>
       <c r="AR19">
-        <v>58.38168938666759</v>
+        <v>58.46282752902156</v>
       </c>
       <c r="AS19">
         <v>13.84810292354515</v>
       </c>
       <c r="AT19">
-        <v>1.280722527085971</v>
+        <v>1.254108635097493</v>
       </c>
       <c r="AU19">
         <v>79.38300684485017</v>
@@ -3112,7 +3112,7 @@
         <v>6079.333988121729</v>
       </c>
       <c r="E21">
-        <v>110.7099994978057</v>
+        <v>111.6841786858975</v>
       </c>
       <c r="F21">
         <v>306.3596955787229</v>
@@ -3230,46 +3230,46 @@
         </is>
       </c>
       <c r="B22">
-        <v>593.4518074934674</v>
+        <v>598.099026136863</v>
       </c>
       <c r="C22">
-        <v>188.5875488951804</v>
+        <v>187.5279418862192</v>
       </c>
       <c r="D22">
-        <v>5856.357215341963</v>
+        <v>5871.712010923536</v>
       </c>
       <c r="E22">
-        <v>412.6389472863771</v>
+        <v>410.9226074131732</v>
       </c>
       <c r="F22">
-        <v>516.8807782335937</v>
+        <v>529.2239435381712</v>
       </c>
       <c r="G22">
-        <v>75.61454123838504</v>
+        <v>76.26459780762698</v>
       </c>
       <c r="H22">
         <v>12.48128356724007</v>
       </c>
       <c r="I22">
-        <v>186.0801891307704</v>
+        <v>187.34057154739</v>
       </c>
       <c r="J22">
-        <v>47.02178090579927</v>
+        <v>47.76926438771095</v>
       </c>
       <c r="K22">
-        <v>1.20385017788511E-14</v>
+        <v>1.346280477148471E-14</v>
       </c>
       <c r="L22">
-        <v>2555.19149116263</v>
+        <v>2567.806980492813</v>
       </c>
       <c r="M22">
-        <v>2153.068990731436</v>
+        <v>2167.595376262352</v>
       </c>
       <c r="N22">
-        <v>980.3972933387452</v>
+        <v>982.4117326073801</v>
       </c>
       <c r="O22">
-        <v>329.0247788671329</v>
+        <v>328.298264236902</v>
       </c>
       <c r="P22">
         <v>14.82878063067461</v>
@@ -3278,28 +3278,28 @@
         <v>0.02751221529950105</v>
       </c>
       <c r="S22">
-        <v>44.0796664136743</v>
+        <v>43.91517398945569</v>
       </c>
       <c r="T22">
-        <v>65.38933080137329</v>
+        <v>65.44874159274784</v>
       </c>
       <c r="U22">
-        <v>48.12487340179419</v>
+        <v>48.30765569659523</v>
       </c>
       <c r="V22">
-        <v>143.4172425389066</v>
+        <v>148.8488956289028</v>
       </c>
       <c r="W22">
-        <v>199.3113674412031</v>
+        <v>199.9232572692729</v>
       </c>
       <c r="Z22">
-        <v>-1.740015968058004E-14</v>
+        <v>-1.797364857602822E-14</v>
       </c>
       <c r="AA22">
-        <v>16.21553534022619</v>
+        <v>16.84069789227166</v>
       </c>
       <c r="AB22">
-        <v>53.84211623103562</v>
+        <v>54.18424927290354</v>
       </c>
       <c r="AC22">
         <v>-5.116257441633771E-15</v>
@@ -3311,16 +3311,16 @@
         <v>19.53195629128272</v>
       </c>
       <c r="AH22">
-        <v>1626.185746554911</v>
+        <v>1631.083861045131</v>
       </c>
       <c r="AJ22">
-        <v>36.15014201508941</v>
+        <v>36.42076630682682</v>
       </c>
       <c r="AK22">
-        <v>575.3927118851334</v>
+        <v>584.1680052122923</v>
       </c>
       <c r="AL22">
-        <v>87.50244663049796</v>
+        <v>91.12642154566745</v>
       </c>
       <c r="AM22">
         <v>16.45390103567319</v>
@@ -3329,7 +3329,7 @@
         <v>22.11524453823237</v>
       </c>
       <c r="AO22">
-        <v>71.59530494845382</v>
+        <v>72.35452193394526</v>
       </c>
       <c r="AP22">
         <v>1511.208308682148</v>
@@ -3347,7 +3347,7 @@
         <v>4.594612289655365</v>
       </c>
       <c r="AU22">
-        <v>277.2977506183117</v>
+        <v>279.8644703087885</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3490,7 +3490,7 @@
         <v>7296.571729281768</v>
       </c>
       <c r="E24">
-        <v>681.3059386667695</v>
+        <v>681.3059386667697</v>
       </c>
       <c r="F24">
         <v>711.98827093316</v>
@@ -3629,7 +3629,7 @@
         <v>6245.96571075934</v>
       </c>
       <c r="E25">
-        <v>385.9617756065118</v>
+        <v>385.9617756065114</v>
       </c>
       <c r="F25">
         <v>747.6322196261513</v>
@@ -3768,7 +3768,7 @@
         <v>5506.149992919936</v>
       </c>
       <c r="E26">
-        <v>591.1397280751723</v>
+        <v>591.1397280751709</v>
       </c>
       <c r="F26">
         <v>392.6142546254788</v>
@@ -3883,7 +3883,7 @@
         <v>5673.291404046161</v>
       </c>
       <c r="E27">
-        <v>275.2056963788302</v>
+        <v>275.2056963788301</v>
       </c>
       <c r="F27">
         <v>823.497388440289</v>
@@ -4022,7 +4022,7 @@
         <v>7807.271022463207</v>
       </c>
       <c r="E28">
-        <v>141.55996664443</v>
+        <v>141.5599666444296</v>
       </c>
       <c r="F28">
         <v>308.7471887201735</v>
